--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
   <si>
     <t>Desis</t>
   </si>
@@ -108,11 +108,11 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,32 +418,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" customWidth="1"/>
-    <col min="4" max="4" width="15.6328125" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" customWidth="1"/>
-    <col min="9" max="9" width="17.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>12114171</v>
       </c>
       <c r="D2" t="s">
@@ -456,11 +456,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>8832480</v>
       </c>
       <c r="D3" t="s">
@@ -479,82 +479,82 @@
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2181646</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>2801081</v>
       </c>
       <c r="E5">
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>11692164</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>7153263</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>40533</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>2633843</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -562,7 +562,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -570,7 +570,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -578,12 +578,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -591,7 +591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -599,7 +599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>2</v>
       </c>
@@ -607,12 +607,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -620,7 +620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -628,7 +628,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -636,21 +636,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -675,19 +675,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>3</v>
       </c>
       <c r="B33">
         <v>1681522</v>
       </c>
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
       <c r="E33">
         <v>0.87568533371104096</v>
       </c>
-      <c r="F33" s="3"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F33" s="2"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -698,7 +701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>2</v>
       </c>
@@ -709,15 +712,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>3</v>
       </c>
       <c r="B38">
         <v>1681522</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>153973</v>
       </c>
@@ -735,7 +741,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -744,7 +750,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -561,6 +561,9 @@
       <c r="D14" t="s">
         <v>13</v>
       </c>
+      <c r="I14">
+        <v>703337100</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -569,6 +572,9 @@
       <c r="D15" t="s">
         <v>6</v>
       </c>
+      <c r="I15">
+        <v>347729699</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -576,6 +582,9 @@
       </c>
       <c r="D16" t="s">
         <v>10</v>
+      </c>
+      <c r="I16">
+        <v>25692000</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -418,19 +418,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.21875" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.54296875" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -439,7 +439,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -456,12 +456,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>8832480</v>
+        <v>8142771</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -479,7 +479,7 @@
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -490,7 +490,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -501,10 +501,10 @@
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -515,29 +515,29 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="3">
-        <v>7153263</v>
+        <v>7353263</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="3">
-        <v>40533</v>
+        <v>40379</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -545,7 +545,7 @@
         <v>2633843</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
@@ -554,7 +554,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -565,7 +565,7 @@
         <v>703337100</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -576,7 +576,7 @@
         <v>347729699</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -587,12 +587,12 @@
         <v>25692000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -600,7 +600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -608,7 +608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>2</v>
       </c>
@@ -616,12 +616,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -629,7 +629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -637,7 +637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -645,12 +645,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>14</v>
       </c>
@@ -659,7 +659,7 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -670,7 +670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -684,7 +684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -699,7 +699,7 @@
       </c>
       <c r="F33" s="2"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -710,7 +710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>2</v>
       </c>
@@ -721,7 +721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -732,7 +732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B41">
         <v>153973</v>
       </c>
@@ -750,7 +750,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -759,7 +759,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -418,19 +418,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" customWidth="1"/>
-    <col min="4" max="4" width="15.6328125" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" customWidth="1"/>
-    <col min="9" max="9" width="17.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -439,7 +439,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -456,7 +456,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -479,7 +479,7 @@
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -490,7 +490,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -501,10 +501,10 @@
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -515,7 +515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -526,7 +526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -537,15 +537,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="3">
-        <v>2633843</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1529252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
@@ -554,7 +554,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -565,7 +565,7 @@
         <v>703337100</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -576,7 +576,7 @@
         <v>347729699</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -587,12 +587,12 @@
         <v>25692000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -600,7 +600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -608,7 +608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>2</v>
       </c>
@@ -616,12 +616,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -629,7 +629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -637,7 +637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -645,12 +645,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>14</v>
       </c>
@@ -659,7 +659,7 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -670,7 +670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -684,7 +684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -699,7 +699,7 @@
       </c>
       <c r="F33" s="2"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -710,7 +710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>2</v>
       </c>
@@ -721,7 +721,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -732,7 +732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>153973</v>
       </c>
@@ -750,7 +750,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -759,7 +759,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="19">
   <si>
     <t>Desis</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>read one by one</t>
+  </si>
+  <si>
+    <t>Scalability-single query</t>
   </si>
 </sst>
 </file>
@@ -105,12 +108,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -417,333 +430,415 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.21875" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
-        <v>12114171</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="4">
+        <v>16657760</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4">
+        <v>20194510</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.80491777130432E-3</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>8142771</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="4">
         <v>8889000</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="4">
         <v>9073877</v>
       </c>
-      <c r="H3">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4">
         <v>7780121</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="4">
         <v>2991545</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
         <v>2181646</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>2801081</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>2769333</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3"/>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
+        <v>6002416</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4">
+        <v>7353263</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4">
+        <v>40379</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1529252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2">
         <v>11692164</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D15" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="6">
+        <v>7480600</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1681522</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2">
+        <v>11692164</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="6">
+        <v>7480600</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1681522</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2">
+        <v>11692164</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="6">
+        <v>7480600</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.87568533371104096</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="2">
+        <v>1681522</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2">
+        <v>11692164</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="6">
+        <v>7480600</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="2">
+        <v>1681522</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="3">
-        <v>7353263</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="3">
-        <v>40379</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="D47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="3">
-        <v>1529252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14">
-        <v>703337100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="D51" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15">
-        <v>347729699</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D52" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I16">
-        <v>25692000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D56" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="D57" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31">
-        <v>11692164</v>
-      </c>
-      <c r="D31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" s="1">
-        <v>7480600</v>
-      </c>
-      <c r="D32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33">
-        <v>1681522</v>
-      </c>
-      <c r="D33" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33">
-        <v>0.87568533371104096</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36">
-        <v>11692164</v>
-      </c>
-      <c r="D36" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>2</v>
-      </c>
-      <c r="B37" s="1">
-        <v>7480600</v>
-      </c>
-      <c r="D37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38">
-        <v>1681522</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B41">
-        <v>153973</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A30:E30"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
   <si>
     <t>Desis</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>read one by one</t>
-  </si>
-  <si>
-    <t>Scalability-single query</t>
   </si>
 </sst>
 </file>
@@ -108,22 +105,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -430,422 +417,340 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="10.1796875" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.54296875" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="1"/>
-      <c r="G1" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>12114171</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>8142771</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1">
+        <v>8889000</v>
+      </c>
+      <c r="F3" s="1">
+        <v>9073877</v>
+      </c>
+      <c r="H3">
+        <v>7780121</v>
+      </c>
+      <c r="I3">
+        <v>2991545</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2181646</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2801081</v>
+      </c>
+      <c r="E5">
+        <v>2769333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3">
+        <v>11692164</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3">
+        <v>7353263</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3">
+        <v>40379</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1529252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14">
+        <v>703337100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15">
+        <v>347729699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>25692000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31">
+        <v>11692164</v>
+      </c>
+      <c r="D31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="1">
+        <v>7480600</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>1681522</v>
+      </c>
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33">
+        <v>0.87568533371104096</v>
+      </c>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
-        <v>16657760</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B36">
+        <v>11692164</v>
+      </c>
+      <c r="D36" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4">
-        <v>20194510</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1.80491777130432E-3</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4">
-        <v>8142771</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="4">
-        <v>8889000</v>
-      </c>
-      <c r="F3" s="4">
-        <v>9073877</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4">
-        <v>7780121</v>
-      </c>
-      <c r="I3" s="4">
-        <v>2991545</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
-        <v>2181646</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B37" s="1">
+        <v>7480600</v>
+      </c>
+      <c r="D37" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
-        <v>2801081</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2769333</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="4">
-        <v>6002416</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="4">
-        <v>7353263</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B38">
+        <v>1681522</v>
+      </c>
+      <c r="D38" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4">
-        <v>40379</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="4">
-        <v>1529252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="2">
-        <v>11692164</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="6">
-        <v>7480600</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="2">
-        <v>1681522</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="2">
-        <v>11692164</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" s="6">
-        <v>7480600</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1681522</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="2">
-        <v>11692164</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="6">
-        <v>7480600</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0.87568533371104096</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="2">
-        <v>1681522</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="2">
-        <v>11692164</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" s="6">
-        <v>7480600</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="2">
-        <v>1681522</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>3</v>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B41">
+        <v>153973</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A13:D13"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A30:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -854,7 +759,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="19">
   <si>
     <t>Desis</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>read one by one</t>
+  </si>
+  <si>
+    <t>Scalability-single query</t>
   </si>
 </sst>
 </file>
@@ -105,12 +108,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -417,340 +430,422 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I59"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" customWidth="1"/>
-    <col min="4" max="4" width="15.6328125" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" customWidth="1"/>
-    <col min="9" max="9" width="17.6328125" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
-        <v>12114171</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="4">
+        <v>16657760</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4">
+        <v>20194510</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.80491777130432E-3</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>8142771</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="4">
         <v>8889000</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="4">
         <v>9073877</v>
       </c>
-      <c r="H3">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4">
         <v>7780121</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="4">
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
         <v>2181646</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>2801081</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
+        <v>6002416</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4">
+        <v>7353263</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4">
+        <v>40379</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1529252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2">
         <v>11692164</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D15" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="6">
+        <v>7480600</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1681522</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2">
+        <v>11692164</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="6">
+        <v>7480600</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1681522</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2">
+        <v>11692164</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="6">
+        <v>7480600</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.87568533371104096</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="2">
+        <v>1681522</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2">
+        <v>11692164</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="6">
+        <v>7480600</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="2">
+        <v>1681522</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="3">
-        <v>7353263</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="3">
-        <v>40379</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="D47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="3">
-        <v>1529252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14">
-        <v>703337100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="D51" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15">
-        <v>347729699</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D52" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I16">
-        <v>25692000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D56" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="D57" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31">
-        <v>11692164</v>
-      </c>
-      <c r="D31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" s="1">
-        <v>7480600</v>
-      </c>
-      <c r="D32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33">
-        <v>1681522</v>
-      </c>
-      <c r="D33" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33">
-        <v>0.87568533371104096</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36">
-        <v>11692164</v>
-      </c>
-      <c r="D36" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>2</v>
-      </c>
-      <c r="B37" s="1">
-        <v>7480600</v>
-      </c>
-      <c r="D37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38">
-        <v>1681522</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B41">
-        <v>153973</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A30:E30"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -759,7 +854,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="29">
   <si>
     <t>Desis</t>
   </si>
@@ -73,6 +73,36 @@
   </si>
   <si>
     <t>Scalability-single query</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>2M</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>4M</t>
+  </si>
+  <si>
+    <t>5M</t>
+  </si>
+  <si>
+    <t>6M</t>
+  </si>
+  <si>
+    <t>7M</t>
+  </si>
+  <si>
+    <t>8M</t>
+  </si>
+  <si>
+    <t>9M</t>
+  </si>
+  <si>
+    <t>10M</t>
   </si>
 </sst>
 </file>
@@ -114,9 +144,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -124,6 +151,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -430,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
@@ -447,12 +477,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>15</v>
@@ -462,17 +492,17 @@
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>16657760</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3">
         <v>20194510</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>1.80491777130432E-3</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -486,23 +516,23 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>8142771</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>8889000</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>9073877</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3">
         <v>7780121</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>2991545</v>
       </c>
     </row>
@@ -510,7 +540,7 @@
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2181646</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -521,21 +551,21 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>2801081</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>2769333</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>6002416</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -546,7 +576,7 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>7353263</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -557,7 +587,7 @@
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>40379</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -568,17 +598,17 @@
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>1529252</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -588,6 +618,24 @@
       <c r="C14" s="2">
         <v>2</v>
       </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2">
+        <v>6</v>
+      </c>
+      <c r="H14" s="2">
+        <v>7</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -596,7 +644,7 @@
       <c r="B15" s="2">
         <v>11692164</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -604,146 +652,178 @@
       <c r="A16" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>7480600</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="2">
         <v>1681522</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B20" s="2">
         <v>11692164</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>7480600</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="2">
         <v>1681522</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B26" s="2">
         <v>11692164</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B27" s="5">
         <v>7480600</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="2">
+      <c r="N27" s="2">
         <v>0.87568533371104096</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B28" s="2">
         <v>1681522</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="L28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B31" s="2">
         <v>11692164</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="L31" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B32" s="5">
         <v>7480600</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B33" s="2">
         <v>1681522</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
@@ -751,7 +831,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>1</v>
       </c>
@@ -759,7 +839,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>2</v>
       </c>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>Desis</t>
   </si>
@@ -51,15 +51,6 @@
     <t xml:space="preserve">size 1 sec </t>
   </si>
   <si>
-    <t>avg ?</t>
-  </si>
-  <si>
-    <t>avg  + sum</t>
-  </si>
-  <si>
-    <t>tumbling + session</t>
-  </si>
-  <si>
     <t>Network-single query</t>
   </si>
   <si>
@@ -75,34 +66,34 @@
     <t>Scalability-single query</t>
   </si>
   <si>
-    <t>1M</t>
-  </si>
-  <si>
-    <t>2M</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>4M</t>
-  </si>
-  <si>
-    <t>5M</t>
-  </si>
-  <si>
-    <t>6M</t>
-  </si>
-  <si>
-    <t>7M</t>
-  </si>
-  <si>
-    <t>8M</t>
-  </si>
-  <si>
-    <t>9M</t>
+    <t>Root</t>
+  </si>
+  <si>
+    <t>Inter</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Total(Byte)</t>
   </si>
   <si>
     <t>10M</t>
+  </si>
+  <si>
+    <t>max  + median</t>
+  </si>
+  <si>
+    <t>tumbling  + tumbling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">size ? sec </t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -118,12 +109,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -138,9 +135,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -154,6 +154,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -460,462 +466,568 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.77734375" style="2" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
     <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>16657760</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4">
         <v>20194510</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="4">
         <v>1.80491777130432E-3</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>8142771</v>
+      <c r="B3" s="4">
+        <v>9398916</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>8889000</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>9073877</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4">
         <v>7780121</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="4">
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>2181646</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>2801081</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>6002416</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>7353263</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>40379</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>1529252</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F11" s="4">
+        <v>2181646</v>
+      </c>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>1</v>
       </c>
       <c r="C14" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="G14" s="2">
-        <v>6</v>
+        <v>500</v>
       </c>
       <c r="H14" s="2">
-        <v>7</v>
-      </c>
-      <c r="I14" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="9">
+        <v>16657760</v>
+      </c>
+      <c r="C15" s="9">
+        <v>13688831</v>
+      </c>
+      <c r="E15" s="9">
+        <v>12696323</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4">
+        <v>9398916</v>
+      </c>
+      <c r="C16" s="4">
+        <v>9705913</v>
+      </c>
+      <c r="E16" s="4">
+        <v>8932279</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="7">
+        <v>1</v>
+      </c>
+      <c r="C21" s="7">
+        <v>10</v>
+      </c>
+      <c r="D21" s="7">
+        <v>50</v>
+      </c>
+      <c r="E21" s="7">
+        <v>100</v>
+      </c>
+      <c r="F21" s="7">
+        <v>200</v>
+      </c>
+      <c r="G21" s="7">
+        <v>500</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="1"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="4">
+        <v>16657760</v>
+      </c>
+      <c r="C30" s="4">
+        <v>32303493</v>
+      </c>
+      <c r="D30" s="4">
+        <v>49336211</v>
+      </c>
+      <c r="E30" s="4">
+        <v>65264851</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="4">
+        <v>2181646</v>
+      </c>
+      <c r="C31" s="4">
+        <v>4321033</v>
+      </c>
+      <c r="D31" s="4">
+        <v>6148562</v>
+      </c>
+      <c r="E31" s="4">
+        <v>8207567</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="4">
+        <v>2801081</v>
+      </c>
+      <c r="C32" s="4">
+        <v>2794906</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2794388</v>
+      </c>
+      <c r="E32" s="4">
+        <v>2910855</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F33" s="7"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="4">
+        <v>6002416</v>
+      </c>
+      <c r="C35" s="9">
+        <v>2905042</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="4">
+        <v>40379</v>
+      </c>
+      <c r="C36" s="4">
+        <v>80613</v>
+      </c>
+      <c r="D36" s="4">
+        <v>120920</v>
+      </c>
+      <c r="E36" s="4">
+        <v>162919</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="4">
+        <v>1529252</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1518300</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1486262</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1461791</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2">
         <v>11692164</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="E41" s="6">
+        <v>75581</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B42" s="6">
         <v>7480600</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="E42" s="6">
+        <v>75532</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B43" s="2">
         <v>1681522</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="E43" s="6">
+        <v>62767</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="2">
-        <v>11692164</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" s="5">
-        <v>7480600</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1681522</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="F45" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="2">
-        <v>11692164</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" s="5">
-        <v>7480600</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="2">
-        <v>0.87568533371104096</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="2">
-        <v>1681522</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="2">
-        <v>11692164</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" s="5">
-        <v>7480600</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="2">
-        <v>1681522</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B46" s="2">
+        <v>11692164</v>
+      </c>
+      <c r="E46" s="6">
+        <v>330441296</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="B47" s="6">
+        <v>7480600</v>
+      </c>
+      <c r="E47" s="6">
+        <v>351385064</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>3</v>
+      <c r="B48" s="2">
+        <v>1681522</v>
+      </c>
+      <c r="E48" s="6">
+        <v>256727468</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020" tabRatio="532"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="28">
   <si>
     <t>Desis</t>
   </si>
@@ -94,6 +94,12 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>VM?</t>
+  </si>
+  <si>
+    <t>8nodes or more</t>
   </si>
 </sst>
 </file>
@@ -109,7 +115,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -119,6 +125,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -135,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -156,10 +168,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -467,34 +488,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.81640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="2"/>
+    <col min="11" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -518,7 +539,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -542,7 +563,7 @@
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -553,7 +574,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -564,10 +585,10 @@
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -578,7 +599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -589,7 +610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
@@ -600,7 +621,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -608,21 +629,21 @@
         <v>1529252</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="F11" s="4">
         <v>2181646</v>
       </c>
       <c r="K11" s="6"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B14" s="2">
         <v>1</v>
       </c>
@@ -645,41 +666,41 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <v>16657760</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>13688831</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>12696323</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="12">
         <v>9398916</v>
       </c>
-      <c r="C16" s="4">
-        <v>9705913</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="C16" s="12">
+        <v>9605913</v>
+      </c>
+      <c r="E16" s="12">
         <v>8932279</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>2</v>
       </c>
@@ -687,12 +708,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B21" s="7">
         <v>1</v>
       </c>
@@ -715,7 +736,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -723,7 +744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
@@ -731,7 +752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>2</v>
       </c>
@@ -739,22 +760,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
       <c r="E28" s="1"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B29" s="2">
         <v>1</v>
       </c>
@@ -767,8 +788,11 @@
       <c r="E29" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G29" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>0</v>
       </c>
@@ -788,7 +812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>2</v>
       </c>
@@ -809,7 +833,7 @@
       </c>
       <c r="G31" s="4"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>3</v>
       </c>
@@ -829,21 +853,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F33" s="7"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B35" s="4">
         <v>6002416</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="8">
         <v>2905042</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -856,7 +880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>2</v>
       </c>
@@ -876,7 +900,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>3</v>
       </c>
@@ -896,15 +920,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
@@ -920,50 +944,53 @@
       <c r="F40" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G40" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="11">
         <v>11692164</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="10">
         <v>75581</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="10">
         <v>7480600</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="10">
         <v>75532</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="11">
         <v>1681522</v>
       </c>
-      <c r="E43" s="6">
-        <v>62767</v>
+      <c r="E43" s="10">
+        <v>245524814</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>16</v>
       </c>
@@ -980,42 +1007,42 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="11">
         <v>11692164</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="10">
         <v>330441296</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="10">
         <v>7480600</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="10">
         <v>351385064</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="11">
         <v>1681522</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="10">
         <v>256727468</v>
       </c>
       <c r="F48" s="2" t="s">
@@ -1037,7 +1064,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1046,7 +1073,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -115,7 +115,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,8 +134,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -143,11 +149,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -171,16 +192,19 @@
     <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -504,23 +528,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
-        <v>16657760</v>
+      <c r="B2" s="13">
+        <v>30545075.399999999</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -540,10 +564,10 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="13">
         <v>9398916</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -564,10 +588,10 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="13">
         <v>2181646</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -575,10 +599,10 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="13">
         <v>2801081</v>
       </c>
       <c r="E5" s="4">
@@ -589,21 +613,21 @@
       <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="4">
-        <v>6002416</v>
+      <c r="B7" s="13">
+        <v>7401292</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="13">
         <v>7353263</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -611,10 +635,10 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="13">
         <v>40379</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -622,10 +646,10 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="13">
         <v>1529252</v>
       </c>
     </row>
@@ -636,142 +660,193 @@
       <c r="K11" s="6"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B14" s="2">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12">
         <v>1</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="12">
         <v>10</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="12">
         <v>50</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="12">
         <v>100</v>
       </c>
-      <c r="F14" s="2">
-        <v>200</v>
-      </c>
-      <c r="G14" s="2">
+      <c r="F14" s="12">
         <v>500</v>
       </c>
-      <c r="H14" s="2">
+      <c r="G14" s="12">
         <v>1000</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="8">
-        <v>16657760</v>
-      </c>
-      <c r="C15" s="8">
-        <v>13688831</v>
-      </c>
-      <c r="E15" s="8">
-        <v>12696323</v>
+      <c r="B15" s="13">
+        <v>30545075.399999999</v>
+      </c>
+      <c r="C15" s="13">
+        <v>30170030.661380101</v>
+      </c>
+      <c r="D15" s="13">
+        <v>29975328.866937201</v>
+      </c>
+      <c r="E15" s="13">
+        <v>29993363.038345698</v>
+      </c>
+      <c r="F15" s="13">
+        <v>30042764.404131401</v>
+      </c>
+      <c r="G15" s="13">
+        <v>30084216.821240999</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="12">
-        <v>9398916</v>
-      </c>
-      <c r="C16" s="12">
-        <v>9605913</v>
-      </c>
-      <c r="E16" s="12">
-        <v>8932279</v>
+      <c r="B16" s="13">
+        <v>9289379.0299999993</v>
+      </c>
+      <c r="C16" s="13">
+        <v>9294990.6999999993</v>
+      </c>
+      <c r="D16" s="13">
+        <v>9154596.3399999999</v>
+      </c>
+      <c r="E16" s="13">
+        <v>9221778.2200000007</v>
+      </c>
+      <c r="F16" s="13">
+        <v>9226710</v>
+      </c>
+      <c r="G16" s="13">
+        <v>9189027.4299999997</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="12" t="s">
         <v>2</v>
       </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
       <c r="I17" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="12" t="s">
         <v>3</v>
       </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B21" s="7">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12">
         <v>1</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="12">
         <v>10</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="12">
         <v>50</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="12">
         <v>100</v>
       </c>
-      <c r="F21" s="7">
-        <v>200</v>
-      </c>
-      <c r="G21" s="7">
+      <c r="F21" s="12">
         <v>500</v>
       </c>
-      <c r="H21" s="7">
+      <c r="G21" s="12">
         <v>1000</v>
       </c>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="12" t="s">
         <v>0</v>
       </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
       <c r="I22" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="12" t="s">
         <v>1</v>
       </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
       <c r="I23" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="12" t="s">
         <v>2</v>
       </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
       <c r="I24" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="12" t="s">
         <v>3</v>
       </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
       <c r="E28" s="1"/>
       <c r="H28" s="4"/>
     </row>
@@ -921,12 +996,12 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B40" s="2" t="s">
@@ -952,10 +1027,10 @@
       <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="10">
         <v>11692164</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="9">
         <v>75581</v>
       </c>
       <c r="F41" s="2" t="s">
@@ -966,10 +1041,10 @@
       <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="9">
         <v>7480600</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="9">
         <v>75532</v>
       </c>
       <c r="F42" s="2" t="s">
@@ -980,10 +1055,10 @@
       <c r="A43" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <v>1681522</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="9">
         <v>245524814</v>
       </c>
       <c r="F43" s="2" t="s">
@@ -1011,10 +1086,10 @@
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="10">
         <v>11692164</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="9">
         <v>330441296</v>
       </c>
       <c r="F46" s="2" t="s">
@@ -1025,10 +1100,10 @@
       <c r="A47" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="9">
         <v>7480600</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="9">
         <v>351385064</v>
       </c>
       <c r="F47" s="2" t="s">
@@ -1039,10 +1114,10 @@
       <c r="A48" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="10">
         <v>1681522</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="9">
         <v>256727468</v>
       </c>
       <c r="F48" s="2" t="s">

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020" tabRatio="532"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,18 +115,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -189,22 +183,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -512,38 +506,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.81640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.6328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.90625" style="2"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="11">
         <v>30545075.399999999</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -563,11 +557,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>9398916</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -587,270 +581,270 @@
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <v>2181646</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>2801081</v>
       </c>
       <c r="E5" s="4">
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>7401292</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>7353263</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>40379</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>1529252</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F11" s="4">
         <v>2181646</v>
       </c>
       <c r="K11" s="6"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10">
         <v>1</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="10">
         <v>10</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="10">
         <v>50</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="10">
         <v>100</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="10">
         <v>500</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="10">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="11">
         <v>30545075.399999999</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="11">
         <v>30170030.661380101</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="11">
         <v>29975328.866937201</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="11">
         <v>29993363.038345698</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="11">
         <v>30042764.404131401</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="11">
         <v>30084216.821240999</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <v>9289379.0299999993</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="11">
         <v>9294990.6999999993</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="11">
         <v>9154596.3399999999</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="11">
         <v>9221778.2200000007</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="11">
         <v>9226710</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="11">
         <v>9189027.4299999997</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
       <c r="I17" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="12" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10">
         <v>1</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="10">
         <v>10</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="10">
         <v>50</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="10">
         <v>100</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="10">
         <v>500</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="10">
         <v>1000</v>
       </c>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="12" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
       <c r="I22" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
       <c r="I23" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
       <c r="I24" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="12" t="s">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
       <c r="E28" s="1"/>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>1</v>
       </c>
@@ -867,7 +861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>0</v>
       </c>
@@ -887,7 +881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>2</v>
       </c>
@@ -908,7 +902,7 @@
       </c>
       <c r="G31" s="4"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>3</v>
       </c>
@@ -928,21 +922,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F33" s="7"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B35" s="4">
         <v>6002416</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="13">
         <v>2905042</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -955,7 +949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>2</v>
       </c>
@@ -975,7 +969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>3</v>
       </c>
@@ -995,15 +989,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="11" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
@@ -1023,49 +1017,49 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <v>11692164</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="8">
         <v>75581</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="8">
         <v>7480600</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="8">
         <v>75532</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <v>1681522</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="8">
         <v>245524814</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>16</v>
       </c>
@@ -1082,42 +1076,42 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <v>11692164</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="8">
         <v>330441296</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="8">
         <v>7480600</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="8">
         <v>351385064</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="9">
         <v>1681522</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="8">
         <v>256727468</v>
       </c>
       <c r="F48" s="2" t="s">
@@ -1139,7 +1133,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1148,7 +1142,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -195,10 +195,10 @@
     <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -522,12 +522,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
@@ -597,7 +597,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="11">
-        <v>2801081</v>
+        <v>3200594.9</v>
       </c>
       <c r="E5" s="4">
         <v>2769333</v>
@@ -654,12 +654,12 @@
       <c r="K11" s="6"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
@@ -738,12 +738,24 @@
       <c r="A17" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="B17" s="11">
+        <v>3200594.9</v>
+      </c>
+      <c r="C17" s="11">
+        <v>843380.47</v>
+      </c>
+      <c r="D17" s="11">
+        <v>244432.04</v>
+      </c>
+      <c r="E17" s="11">
+        <v>142866.29999999999</v>
+      </c>
+      <c r="F17" s="11">
+        <v>57506.04</v>
+      </c>
+      <c r="G17" s="11">
+        <v>48292.25</v>
+      </c>
       <c r="I17" s="2" t="s">
         <v>24</v>
       </c>
@@ -835,12 +847,12 @@
       <c r="G25" s="11"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
       <c r="E28" s="1"/>
       <c r="H28" s="4"/>
     </row>
@@ -936,7 +948,7 @@
       <c r="B35" s="4">
         <v>6002416</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="12">
         <v>2905042</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -990,12 +1002,12 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020" tabRatio="532"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="29">
   <si>
     <t>Desis</t>
   </si>
@@ -81,9 +81,6 @@
     <t>Total(Byte)</t>
   </si>
   <si>
-    <t>10M</t>
-  </si>
-  <si>
     <t>max  + median</t>
   </si>
   <si>
@@ -96,10 +93,16 @@
     <t>?</t>
   </si>
   <si>
-    <t>VM?</t>
-  </si>
-  <si>
-    <t>8nodes or more</t>
+    <t>HOL:4000,4999;1.650478445196E12,1.650475774442E12,1.650478276451E12,1.650476221049E12,1.650477132239</t>
+  </si>
+  <si>
+    <t>1671E12,1.650476738812E12,1.650476337396E12,1.650475519069E12,1.650478181548E12,1.650478230193E12:-2</t>
+  </si>
+  <si>
+    <t>100M</t>
+  </si>
+  <si>
+    <t>byte</t>
   </si>
 </sst>
 </file>
@@ -115,18 +118,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -162,12 +159,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -183,22 +177,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -505,49 +505,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P53"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.36328125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="2"/>
+    <col min="11" max="14" width="8.90625" style="2"/>
+    <col min="15" max="15" width="15.1796875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="21.08984375" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="8">
         <v>30545075.399999999</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3">
         <v>20194510</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>1.80491777130432E-3</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -557,576 +560,655 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="8">
         <v>9398916</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>8889000</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>9073877</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3">
         <v>7780121</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="8">
         <v>2181646</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="8">
         <v>3200594.9</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="8">
         <v>7401292</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="8">
         <v>7353263</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="8">
         <v>40379</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="8">
         <v>1529252</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="F11" s="4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F11" s="3">
         <v>2181646</v>
       </c>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
+      <c r="K11" s="5"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7">
         <v>1</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="7">
         <v>10</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="7">
         <v>50</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="7">
         <v>100</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="7">
         <v>500</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="7">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="8">
         <v>30545075.399999999</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="8">
         <v>30170030.661380101</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="8">
         <v>29975328.866937201</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="8">
         <v>29993363.038345698</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="8">
         <v>30042764.404131401</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="8">
         <v>30084216.821240999</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="8">
         <v>9289379.0299999993</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>9294990.6999999993</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="8">
         <v>9154596.3399999999</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="8">
         <v>9221778.2200000007</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="8">
         <v>9226710</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="8">
         <v>9189027.4299999997</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="8">
+        <v>2181646</v>
+      </c>
+      <c r="C17" s="12">
+        <v>2124146.77</v>
+      </c>
+      <c r="D17" s="12">
+        <v>2071365.54</v>
+      </c>
+      <c r="E17" s="12">
+        <v>2032837.0870000001</v>
+      </c>
+      <c r="F17" s="12">
+        <v>2058517.16</v>
+      </c>
+      <c r="G17" s="12">
+        <v>2092535.16</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="8">
         <v>3200594.9</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C18" s="8">
         <v>843380.47</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D18" s="8">
         <v>244432.04</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E18" s="8">
         <v>142866.29999999999</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F18" s="8">
         <v>57506.04</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G18" s="8">
         <v>48292.25</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10">
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7">
         <v>1</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="7">
         <v>10</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="7">
         <v>50</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="7">
         <v>100</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="7">
         <v>500</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="7">
         <v>1000</v>
       </c>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
       <c r="I22" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
       <c r="I23" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
       <c r="I24" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="13">
+        <v>11692164</v>
+      </c>
+      <c r="C31" s="13">
+        <v>116</v>
+      </c>
+      <c r="D31" s="13">
+        <v>116</v>
+      </c>
+      <c r="E31" s="13">
+        <v>232</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="13">
+        <v>7480600</v>
+      </c>
+      <c r="C32" s="13">
+        <v>3478</v>
+      </c>
+      <c r="D32" s="13">
+        <v>3478</v>
+      </c>
+      <c r="E32" s="13">
+        <v>6956</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="13">
+        <v>1681522</v>
+      </c>
+      <c r="C33" s="13">
+        <v>1601200000</v>
+      </c>
+      <c r="D33" s="13">
+        <v>1601200000</v>
+      </c>
+      <c r="E33" s="13">
+        <v>3202400000</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="13">
+        <v>11692164</v>
+      </c>
+      <c r="C36" s="13">
+        <v>1600012168</v>
+      </c>
+      <c r="D36" s="13">
+        <v>1601200000</v>
+      </c>
+      <c r="E36" s="13">
+        <v>3201212168</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="13">
+        <v>7480600</v>
+      </c>
+      <c r="C37" s="13">
+        <v>1800039616</v>
+      </c>
+      <c r="D37" s="13">
+        <v>1800039616</v>
+      </c>
+      <c r="E37" s="13">
+        <v>3600079232</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="13">
+        <v>1681522</v>
+      </c>
+      <c r="C38" s="13">
+        <v>1601200000</v>
+      </c>
+      <c r="D38" s="13">
+        <v>1601200000</v>
+      </c>
+      <c r="E38" s="13">
+        <v>3202400000</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="1"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="2">
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="1"/>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C45" s="2">
         <v>2</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D45" s="2">
         <v>3</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E45" s="2">
         <v>4</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="4">
-        <v>16657760</v>
-      </c>
-      <c r="C30" s="4">
-        <v>32303493</v>
-      </c>
-      <c r="D30" s="4">
-        <v>49336211</v>
-      </c>
-      <c r="E30" s="4">
-        <v>65264851</v>
-      </c>
-      <c r="F30" s="7" t="s">
+      <c r="F45" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" s="4">
-        <v>2181646</v>
-      </c>
-      <c r="C31" s="4">
-        <v>4321033</v>
-      </c>
-      <c r="D31" s="4">
-        <v>6148562</v>
-      </c>
-      <c r="E31" s="4">
-        <v>8207567</v>
-      </c>
-      <c r="F31" s="7" t="s">
+      <c r="G45" s="2">
+        <v>6</v>
+      </c>
+      <c r="H45" s="2">
+        <v>7</v>
+      </c>
+      <c r="I45" s="2">
         <v>8</v>
       </c>
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="4">
-        <v>2801081</v>
-      </c>
-      <c r="C32" s="4">
-        <v>2794906</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2794388</v>
-      </c>
-      <c r="E32" s="4">
-        <v>2910855</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F33" s="7"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="4">
-        <v>6002416</v>
-      </c>
-      <c r="C35" s="12">
-        <v>2905042</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B36" s="4">
-        <v>40379</v>
-      </c>
-      <c r="C36" s="4">
-        <v>80613</v>
-      </c>
-      <c r="D36" s="4">
-        <v>120920</v>
-      </c>
-      <c r="E36" s="4">
-        <v>162919</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="4">
-        <v>1529252</v>
-      </c>
-      <c r="C37" s="4">
-        <v>1518300</v>
-      </c>
-      <c r="D37" s="4">
-        <v>1486262</v>
-      </c>
-      <c r="E37" s="4">
-        <v>1461791</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="9">
-        <v>11692164</v>
-      </c>
-      <c r="E41" s="8">
-        <v>75581</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B42" s="8">
-        <v>7480600</v>
-      </c>
-      <c r="E42" s="8">
-        <v>75532</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="9">
-        <v>1681522</v>
-      </c>
-      <c r="E43" s="8">
-        <v>245524814</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="9">
-        <v>11692164</v>
-      </c>
-      <c r="E46" s="8">
-        <v>330441296</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="B46" s="8">
+        <v>30545075.399999999</v>
+      </c>
+      <c r="C46" s="3">
+        <v>32303493</v>
+      </c>
+      <c r="D46" s="3">
+        <v>49336211</v>
+      </c>
+      <c r="E46" s="3">
+        <v>65264851</v>
+      </c>
+      <c r="J46" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B47" s="8">
-        <v>7480600</v>
-      </c>
-      <c r="E47" s="8">
-        <v>351385064</v>
-      </c>
-      <c r="F47" s="2" t="s">
+        <v>2181646</v>
+      </c>
+      <c r="C47" s="3">
+        <v>4321033</v>
+      </c>
+      <c r="D47" s="3">
+        <v>6148562</v>
+      </c>
+      <c r="E47" s="3">
+        <v>8207567</v>
+      </c>
+      <c r="J47" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="9">
-        <v>1681522</v>
-      </c>
-      <c r="E48" s="8">
-        <v>256727468</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="B48" s="8">
+        <v>3200594.9</v>
+      </c>
+      <c r="C48" s="3">
+        <v>2794906</v>
+      </c>
+      <c r="D48" s="3">
+        <v>2794388</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2910855</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H49" s="3"/>
+      <c r="J49" s="6"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J50" s="6"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="3">
+        <v>6002416</v>
+      </c>
+      <c r="C51" s="9">
+        <v>2905042</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="3">
+        <v>40379</v>
+      </c>
+      <c r="C52" s="3">
+        <v>80613</v>
+      </c>
+      <c r="D52" s="3">
+        <v>120920</v>
+      </c>
+      <c r="E52" s="3">
+        <v>162919</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="3">
+        <v>1529252</v>
+      </c>
+      <c r="C53" s="3">
+        <v>1518300</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1486262</v>
+      </c>
+      <c r="E53" s="3">
+        <v>1461791</v>
+      </c>
+      <c r="J53" s="6" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1134,8 +1216,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1145,7 +1227,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1154,7 +1236,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020" tabRatio="532"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
   <si>
     <t>Desis</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t xml:space="preserve">size ? sec </t>
-  </si>
-  <si>
-    <t>?</t>
   </si>
   <si>
     <t>HOL:4000,4999;1.650478445196E12,1.650475774442E12,1.650478276451E12,1.650476221049E12,1.650477132239</t>
@@ -183,9 +180,6 @@
     <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -195,10 +189,13 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -505,38 +502,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P62"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.36328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.6328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="14" width="8.90625" style="2"/>
-    <col min="15" max="15" width="15.1796875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="21.08984375" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="8.90625" style="2"/>
+    <col min="11" max="14" width="8.88671875" style="2"/>
+    <col min="15" max="15" width="15.21875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="21.109375" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -560,7 +557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -584,7 +581,7 @@
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
@@ -595,7 +592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
@@ -606,10 +603,10 @@
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
@@ -620,7 +617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
@@ -631,7 +628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
@@ -642,7 +639,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -650,24 +647,24 @@
         <v>1529252</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F11" s="3">
         <v>2181646</v>
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="7">
         <v>10</v>
@@ -685,7 +682,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -711,7 +708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>1</v>
       </c>
@@ -737,33 +734,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="8">
         <v>2181646</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <v>2124146.77</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <v>2071365.54</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="11">
         <v>2032837.0870000001</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="11">
         <v>2058517.16</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="11">
         <v>2092535.16</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>3</v>
       </c>
@@ -786,7 +783,7 @@
         <v>48292.25</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="7">
         <v>1</v>
@@ -808,7 +805,7 @@
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>0</v>
       </c>
@@ -822,7 +819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>1</v>
       </c>
@@ -836,7 +833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>2</v>
       </c>
@@ -850,7 +847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>3</v>
       </c>
@@ -861,356 +858,503 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13" t="s">
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="8" t="s">
         <v>20</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="8">
         <v>11692164</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="8">
         <v>116</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="8">
         <v>116</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="8">
         <v>232</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H31" s="10"/>
+      <c r="H31" s="9"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A32" s="13" t="s">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="8">
         <v>7480600</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="8">
         <v>3478</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="8">
         <v>3478</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="8">
         <v>6956</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A33" s="13" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="8">
         <v>1681522</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="8">
         <v>1601200000</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="8">
         <v>1601200000</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="8">
         <v>3202400000</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A36" s="13" t="s">
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="8">
         <v>11692164</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="8">
         <v>1600012168</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="8">
         <v>1601200000</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="8">
         <v>3201212168</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H36" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="13" t="s">
+      <c r="H36" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="8">
         <v>7480600</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="8">
         <v>1800039616</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="8">
         <v>1800039616</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="8">
         <v>3600079232</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A38" s="13" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="8">
         <v>1681522</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="8">
         <v>1601200000</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="8">
         <v>1601200000</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="8">
         <v>3202400000</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A44" s="11" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
       <c r="E44" s="1"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B45" s="2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="11"/>
+      <c r="B45" s="13">
         <v>1</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="13">
         <v>2</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="13">
         <v>3</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="13">
         <v>4</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="13">
         <v>5</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="13">
         <v>6</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="13">
         <v>7</v>
       </c>
-      <c r="I45" s="2">
+      <c r="I45" s="13">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B46" s="8">
         <v>30545075.399999999</v>
       </c>
-      <c r="C46" s="3">
-        <v>32303493</v>
-      </c>
-      <c r="D46" s="3">
-        <v>49336211</v>
-      </c>
-      <c r="E46" s="3">
-        <v>65264851</v>
+      <c r="C46" s="11">
+        <v>60340061.32</v>
+      </c>
+      <c r="D46" s="8">
+        <v>89925986.609999999</v>
+      </c>
+      <c r="E46" s="11">
+        <v>119973452</v>
+      </c>
+      <c r="F46" s="8">
+        <v>150213822</v>
+      </c>
+      <c r="G46" s="11">
+        <v>180505301</v>
+      </c>
+      <c r="H46" s="8">
+        <v>209827302</v>
+      </c>
+      <c r="I46" s="11">
+        <v>240342115</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B47" s="8">
         <v>2181646</v>
       </c>
-      <c r="C47" s="3">
-        <v>4321033</v>
-      </c>
-      <c r="D47" s="3">
-        <v>6148562</v>
-      </c>
-      <c r="E47" s="3">
-        <v>8207567</v>
+      <c r="C47" s="11">
+        <v>4248293</v>
+      </c>
+      <c r="D47" s="11">
+        <v>6214096.6200000001</v>
+      </c>
+      <c r="E47" s="11">
+        <v>8234068.6399999997</v>
+      </c>
+      <c r="F47" s="11">
+        <v>10462675.800000001</v>
+      </c>
+      <c r="G47" s="8">
+        <v>13089876</v>
+      </c>
+      <c r="H47" s="11">
+        <v>14869027.390000001</v>
+      </c>
+      <c r="I47" s="11">
+        <v>16262696.696</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
         <v>3</v>
       </c>
       <c r="B48" s="8">
         <v>3200594.9</v>
       </c>
-      <c r="C48" s="3">
-        <v>2794906</v>
-      </c>
-      <c r="D48" s="3">
-        <v>2794388</v>
-      </c>
-      <c r="E48" s="3">
-        <v>2910855</v>
+      <c r="C48" s="8">
+        <v>3198892</v>
+      </c>
+      <c r="D48" s="8">
+        <v>3206562</v>
+      </c>
+      <c r="E48" s="8">
+        <v>3188886</v>
+      </c>
+      <c r="F48" s="11">
+        <v>3200231</v>
+      </c>
+      <c r="G48" s="11">
+        <v>3193273</v>
+      </c>
+      <c r="H48" s="11">
+        <v>3192710</v>
+      </c>
+      <c r="I48" s="11">
+        <v>3196070</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
       <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="3">
-        <v>6002416</v>
-      </c>
-      <c r="C51" s="9">
-        <v>2905042</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>24</v>
+      <c r="B51" s="8">
+        <v>7401292</v>
+      </c>
+      <c r="C51" s="8">
+        <v>7439741</v>
+      </c>
+      <c r="D51" s="8">
+        <v>7641958</v>
+      </c>
+      <c r="E51" s="8">
+        <v>7531010</v>
+      </c>
+      <c r="F51" s="8">
+        <v>7664154</v>
+      </c>
+      <c r="G51" s="8">
+        <v>7681207</v>
+      </c>
+      <c r="H51" s="8">
+        <v>7689210</v>
+      </c>
+      <c r="I51" s="8">
+        <v>7689210</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="8">
         <v>40379</v>
       </c>
-      <c r="C52" s="3">
-        <v>80613</v>
-      </c>
-      <c r="D52" s="3">
-        <v>120920</v>
-      </c>
-      <c r="E52" s="3">
-        <v>162919</v>
+      <c r="C52" s="8">
+        <v>81010</v>
+      </c>
+      <c r="D52" s="8">
+        <v>121524</v>
+      </c>
+      <c r="E52" s="8">
+        <v>162212</v>
+      </c>
+      <c r="F52" s="8">
+        <v>202755</v>
+      </c>
+      <c r="G52" s="8">
+        <v>243282</v>
+      </c>
+      <c r="H52" s="8">
+        <v>283521</v>
+      </c>
+      <c r="I52" s="8">
+        <v>324008</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="3">
-        <v>1529252</v>
-      </c>
-      <c r="C53" s="3">
-        <v>1518300</v>
-      </c>
-      <c r="D53" s="3">
-        <v>1486262</v>
-      </c>
-      <c r="E53" s="3">
-        <v>1461791</v>
+      <c r="B53" s="8">
+        <v>1568881</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1554271</v>
+      </c>
+      <c r="D53" s="8">
+        <v>1556244</v>
+      </c>
+      <c r="E53" s="8">
+        <v>1572295</v>
+      </c>
+      <c r="F53" s="8">
+        <v>1561424</v>
+      </c>
+      <c r="G53" s="8">
+        <v>1558847</v>
+      </c>
+      <c r="H53" s="8">
+        <v>1558314</v>
+      </c>
+      <c r="I53" s="8">
+        <v>1561340</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D54" s="12"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="12"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="12"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="12"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="12"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1227,7 +1371,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1236,7 +1380,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020" tabRatio="532"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -503,25 +503,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P62"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.36328125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="14" width="8.88671875" style="2"/>
-    <col min="15" max="15" width="15.21875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="21.109375" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="2"/>
+    <col min="11" max="14" width="8.90625" style="2"/>
+    <col min="15" max="15" width="15.1796875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="21.08984375" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>4</v>
       </c>
@@ -533,7 +533,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -581,7 +581,7 @@
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
@@ -592,7 +592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
@@ -603,10 +603,10 @@
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
@@ -617,7 +617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
@@ -628,7 +628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
@@ -639,7 +639,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -647,13 +647,13 @@
         <v>1529252</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="F11" s="3">
         <v>2181646</v>
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>9</v>
       </c>
@@ -661,7 +661,7 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="7">
         <v>2</v>
@@ -682,7 +682,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -708,7 +708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>1</v>
       </c>
@@ -734,7 +734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>2</v>
       </c>
@@ -760,7 +760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>3</v>
       </c>
@@ -783,7 +783,7 @@
         <v>48292.25</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
       <c r="B21" s="7">
         <v>1</v>
@@ -805,7 +805,7 @@
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>0</v>
       </c>
@@ -819,7 +819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>1</v>
       </c>
@@ -833,7 +833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>2</v>
       </c>
@@ -847,7 +847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>3</v>
       </c>
@@ -858,7 +858,7 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>11</v>
       </c>
@@ -866,7 +866,7 @@
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="8"/>
       <c r="B30" s="8" t="s">
         <v>16</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
@@ -910,7 +910,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>2</v>
       </c>
@@ -930,7 +930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>3</v>
       </c>
@@ -950,14 +950,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="s">
         <v>16</v>
@@ -978,7 +978,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>0</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>2</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>3</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>15</v>
       </c>
@@ -1051,7 +1051,7 @@
       <c r="E44" s="1"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="11"/>
       <c r="B45" s="13">
         <v>1</v>
@@ -1078,7 +1078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
         <v>2</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
         <v>3</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -1185,7 +1185,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -1196,7 +1196,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>2</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>3</v>
       </c>
@@ -1292,10 +1292,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D54" s="12"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C56" s="12"/>
       <c r="D56" s="12"/>
       <c r="E56" s="12"/>
@@ -1303,7 +1303,7 @@
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C57" s="12"/>
       <c r="D57" s="12"/>
       <c r="E57" s="12"/>
@@ -1312,7 +1312,7 @@
       <c r="H57" s="12"/>
       <c r="I57" s="12"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
@@ -1321,7 +1321,7 @@
       <c r="H58" s="10"/>
       <c r="I58" s="12"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="10"/>
@@ -1330,7 +1330,7 @@
       <c r="H59" s="10"/>
       <c r="I59" s="12"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="10"/>
@@ -1339,7 +1339,7 @@
       <c r="H60" s="10"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="10"/>
@@ -1348,7 +1348,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="12"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
       <c r="E62" s="10"/>
@@ -1371,7 +1371,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1380,7 +1380,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020" tabRatio="532"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -156,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -196,6 +196,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -503,25 +506,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P62"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.36328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.6328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="14" width="8.90625" style="2"/>
-    <col min="15" max="15" width="15.1796875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="21.08984375" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="8.90625" style="2"/>
+    <col min="11" max="14" width="8.88671875" style="2"/>
+    <col min="15" max="15" width="15.21875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="21.109375" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>4</v>
       </c>
@@ -533,11 +536,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="15">
         <v>30545075.399999999</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -557,11 +560,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="15">
         <v>9398916</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -581,79 +584,79 @@
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="15">
         <v>2181646</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8">
-        <v>3200594.9</v>
+      <c r="B5" s="15">
+        <v>3065244.36</v>
       </c>
       <c r="E5" s="3">
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="15">
         <v>7401292</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="15">
         <v>7353263</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="15">
         <v>40379</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="8">
-        <v>1529252</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B10" s="15">
+        <v>1626861.2661948199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F11" s="3">
         <v>2181646</v>
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>9</v>
       </c>
@@ -661,7 +664,7 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7">
         <v>2</v>
@@ -682,108 +685,108 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="15">
         <v>30545075.399999999</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="15">
         <v>30170030.661380101</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="15">
         <v>29975328.866937201</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="15">
         <v>29993363.038345698</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="15">
         <v>30042764.404131401</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="15">
         <v>30084216.821240999</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="15">
         <v>9289379.0299999993</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="15">
         <v>9294990.6999999993</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="15">
         <v>9154596.3399999999</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="15">
         <v>9221778.2200000007</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="15">
         <v>9226710</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="15">
         <v>9189027.4299999997</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="15">
         <v>2181646</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="13">
         <v>2124146.77</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="13">
         <v>2071365.54</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="13">
         <v>2032837.0870000001</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="13">
         <v>2058517.16</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="13">
         <v>2092535.16</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="8">
-        <v>3200594.9</v>
-      </c>
-      <c r="C18" s="8">
-        <v>843380.47</v>
-      </c>
-      <c r="D18" s="8">
-        <v>244432.04</v>
-      </c>
-      <c r="E18" s="8">
-        <v>142866.29999999999</v>
-      </c>
-      <c r="F18" s="8">
-        <v>57506.04</v>
-      </c>
-      <c r="G18" s="8">
-        <v>48292.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B18" s="15">
+        <v>2673205.9300000002</v>
+      </c>
+      <c r="C18" s="15">
+        <v>876913.8</v>
+      </c>
+      <c r="D18" s="15">
+        <v>362475.64</v>
+      </c>
+      <c r="E18" s="15">
+        <v>223458.038</v>
+      </c>
+      <c r="F18" s="15">
+        <v>154271.15</v>
+      </c>
+      <c r="G18" s="15">
+        <v>129632.158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="7">
         <v>1</v>
@@ -805,7 +808,7 @@
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>0</v>
       </c>
@@ -819,7 +822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>1</v>
       </c>
@@ -833,7 +836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>2</v>
       </c>
@@ -847,7 +850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>3</v>
       </c>
@@ -858,7 +861,7 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>11</v>
       </c>
@@ -866,7 +869,7 @@
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8" t="s">
         <v>16</v>
@@ -888,7 +891,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
@@ -910,7 +913,7 @@
       <c r="H31" s="9"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>2</v>
       </c>
@@ -930,7 +933,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>3</v>
       </c>
@@ -950,14 +953,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="s">
         <v>16</v>
@@ -978,7 +981,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>0</v>
       </c>
@@ -1001,7 +1004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>2</v>
       </c>
@@ -1021,7 +1024,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>3</v>
       </c>
@@ -1041,7 +1044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>15</v>
       </c>
@@ -1051,7 +1054,7 @@
       <c r="E44" s="1"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="11"/>
       <c r="B45" s="13">
         <v>1</v>
@@ -1078,224 +1081,224 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="15">
         <v>30545075.399999999</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="13">
         <v>60340061.32</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="15">
         <v>89925986.609999999</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="13">
         <v>119973452</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="15">
         <v>150213822</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="13">
         <v>180505301</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="15">
         <v>209827302</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="13">
         <v>240342115</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="15">
         <v>2181646</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="13">
         <v>4248293</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="13">
         <v>6214096.6200000001</v>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="13">
         <v>8234068.6399999997</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="13">
         <v>10462675.800000001</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="15">
         <v>13089876</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="13">
         <v>14869027.390000001</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="13">
         <v>16262696.696</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="8">
-        <v>3200594.9</v>
-      </c>
-      <c r="C48" s="8">
-        <v>3198892</v>
-      </c>
-      <c r="D48" s="8">
-        <v>3206562</v>
-      </c>
-      <c r="E48" s="8">
-        <v>3188886</v>
-      </c>
-      <c r="F48" s="11">
-        <v>3200231</v>
-      </c>
-      <c r="G48" s="11">
-        <v>3193273</v>
-      </c>
-      <c r="H48" s="11">
-        <v>3192710</v>
-      </c>
-      <c r="I48" s="11">
-        <v>3196070</v>
+      <c r="B48" s="15">
+        <v>3065244.36</v>
+      </c>
+      <c r="C48" s="15">
+        <v>3056406.42</v>
+      </c>
+      <c r="D48" s="15">
+        <v>3071268.7</v>
+      </c>
+      <c r="E48" s="15">
+        <v>3057605.98</v>
+      </c>
+      <c r="F48" s="13">
+        <v>3049152.15</v>
+      </c>
+      <c r="G48" s="13">
+        <v>3062044.6</v>
+      </c>
+      <c r="H48" s="13">
+        <v>3068963.78</v>
+      </c>
+      <c r="I48" s="13">
+        <v>3063581.93</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="15">
         <v>7401292</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="15">
         <v>7439741</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="15">
         <v>7641958</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="15">
         <v>7531010</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="15">
         <v>7664154</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="15">
         <v>7681207</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="15">
         <v>7689210</v>
       </c>
-      <c r="I51" s="8">
+      <c r="I51" s="15">
         <v>7689210</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="15">
         <v>40379</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="15">
         <v>81010</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="15">
         <v>121524</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="15">
         <v>162212</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="15">
         <v>202755</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="15">
         <v>243282</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="15">
         <v>283521</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="15">
         <v>324008</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="8">
-        <v>1568881</v>
-      </c>
-      <c r="C53" s="8">
-        <v>1554271</v>
-      </c>
-      <c r="D53" s="8">
-        <v>1556244</v>
-      </c>
-      <c r="E53" s="8">
-        <v>1572295</v>
-      </c>
-      <c r="F53" s="8">
-        <v>1561424</v>
-      </c>
-      <c r="G53" s="8">
-        <v>1558847</v>
-      </c>
-      <c r="H53" s="8">
-        <v>1558314</v>
-      </c>
-      <c r="I53" s="8">
-        <v>1561340</v>
+      <c r="B53" s="15">
+        <v>1626861.2661948199</v>
+      </c>
+      <c r="C53" s="15">
+        <v>1621172.4051846999</v>
+      </c>
+      <c r="D53" s="15">
+        <v>1622474.0689999999</v>
+      </c>
+      <c r="E53" s="15">
+        <v>1626861.2661948199</v>
+      </c>
+      <c r="F53" s="15">
+        <v>1635437.8067000001</v>
+      </c>
+      <c r="G53" s="15">
+        <v>1627743.497</v>
+      </c>
+      <c r="H53" s="15">
+        <v>1624585.38</v>
+      </c>
+      <c r="I53" s="15">
+        <v>1621947.61</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D54" s="12"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C56" s="12"/>
       <c r="D56" s="12"/>
       <c r="E56" s="12"/>
@@ -1303,7 +1306,7 @@
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C57" s="12"/>
       <c r="D57" s="12"/>
       <c r="E57" s="12"/>
@@ -1312,7 +1315,7 @@
       <c r="H57" s="12"/>
       <c r="I57" s="12"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
@@ -1321,7 +1324,7 @@
       <c r="H58" s="10"/>
       <c r="I58" s="12"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
       <c r="E59" s="10"/>
@@ -1330,7 +1333,7 @@
       <c r="H59" s="10"/>
       <c r="I59" s="12"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="10"/>
@@ -1339,7 +1342,7 @@
       <c r="H60" s="10"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
       <c r="E61" s="10"/>
@@ -1348,7 +1351,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="12"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
       <c r="E62" s="10"/>
@@ -1371,7 +1374,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1380,7 +1383,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -195,10 +195,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -525,12 +525,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
@@ -540,7 +540,7 @@
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="14">
         <v>30545075.399999999</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -564,7 +564,7 @@
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="14">
         <v>9398916</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -588,7 +588,7 @@
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>2181646</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -599,7 +599,7 @@
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>3065244.36</v>
       </c>
       <c r="E5" s="3">
@@ -613,7 +613,7 @@
       <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>7401292</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -624,7 +624,7 @@
       <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>7353263</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -635,7 +635,7 @@
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>40379</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -646,7 +646,7 @@
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>1626861.2661948199</v>
       </c>
     </row>
@@ -657,12 +657,12 @@
       <c r="K11" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
@@ -689,22 +689,22 @@
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <v>30545075.399999999</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <v>30170030.661380101</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <v>29975328.866937201</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <v>29993363.038345698</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <v>30042764.404131401</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
         <v>30084216.821240999</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -715,22 +715,22 @@
       <c r="A16" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <v>9289379.0299999993</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <v>9294990.6999999993</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <v>9154596.3399999999</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <v>9221778.2200000007</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <v>9226710</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <v>9189027.4299999997</v>
       </c>
       <c r="I16" s="2" t="s">
@@ -741,7 +741,7 @@
       <c r="A17" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <v>2181646</v>
       </c>
       <c r="C17" s="13">
@@ -767,22 +767,22 @@
       <c r="A18" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <v>2673205.9300000002</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <v>876913.8</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <v>362475.64</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <v>223458.038</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="14">
         <v>154271.15</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <v>129632.158</v>
       </c>
     </row>
@@ -862,12 +862,12 @@
       <c r="G25" s="8"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
@@ -1045,12 +1045,12 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
       <c r="E44" s="1"/>
       <c r="H44" s="3"/>
     </row>
@@ -1085,25 +1085,25 @@
       <c r="A46" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="14">
         <v>30545075.399999999</v>
       </c>
       <c r="C46" s="13">
         <v>60340061.32</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="14">
         <v>89925986.609999999</v>
       </c>
       <c r="E46" s="13">
         <v>119973452</v>
       </c>
-      <c r="F46" s="15">
+      <c r="F46" s="14">
         <v>150213822</v>
       </c>
       <c r="G46" s="13">
         <v>180505301</v>
       </c>
-      <c r="H46" s="15">
+      <c r="H46" s="14">
         <v>209827302</v>
       </c>
       <c r="I46" s="13">
@@ -1117,7 +1117,7 @@
       <c r="A47" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="14">
         <v>2181646</v>
       </c>
       <c r="C47" s="13">
@@ -1132,7 +1132,7 @@
       <c r="F47" s="13">
         <v>10462675.800000001</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="14">
         <v>13089876</v>
       </c>
       <c r="H47" s="13">
@@ -1149,16 +1149,16 @@
       <c r="A48" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="14">
         <v>3065244.36</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="14">
         <v>3056406.42</v>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="14">
         <v>3071268.7</v>
       </c>
-      <c r="E48" s="15">
+      <c r="E48" s="14">
         <v>3057605.98</v>
       </c>
       <c r="F48" s="13">
@@ -1203,28 +1203,28 @@
       <c r="A51" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B51" s="14">
         <v>7401292</v>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="14">
         <v>7439741</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="14">
         <v>7641958</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="14">
         <v>7531010</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="14">
         <v>7664154</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="14">
         <v>7681207</v>
       </c>
-      <c r="H51" s="15">
+      <c r="H51" s="14">
         <v>7689210</v>
       </c>
-      <c r="I51" s="15">
+      <c r="I51" s="14">
         <v>7689210</v>
       </c>
       <c r="J51" s="6" t="s">
@@ -1235,28 +1235,28 @@
       <c r="A52" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="15">
+      <c r="B52" s="14">
         <v>40379</v>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="14">
         <v>81010</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="14">
         <v>121524</v>
       </c>
-      <c r="E52" s="15">
+      <c r="E52" s="14">
         <v>162212</v>
       </c>
-      <c r="F52" s="15">
+      <c r="F52" s="14">
         <v>202755</v>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="14">
         <v>243282</v>
       </c>
-      <c r="H52" s="15">
+      <c r="H52" s="14">
         <v>283521</v>
       </c>
-      <c r="I52" s="15">
+      <c r="I52" s="14">
         <v>324008</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -1267,28 +1267,28 @@
       <c r="A53" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="14">
         <v>1626861.2661948199</v>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="14">
         <v>1621172.4051846999</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="14">
         <v>1622474.0689999999</v>
       </c>
-      <c r="E53" s="15">
+      <c r="E53" s="14">
         <v>1626861.2661948199</v>
       </c>
-      <c r="F53" s="15">
+      <c r="F53" s="14">
         <v>1635437.8067000001</v>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="14">
         <v>1627743.497</v>
       </c>
-      <c r="H53" s="15">
+      <c r="H53" s="14">
         <v>1624585.38</v>
       </c>
-      <c r="I53" s="15">
+      <c r="I53" s="14">
         <v>1621947.61</v>
       </c>
       <c r="J53" s="6" t="s">

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -156,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -199,6 +199,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -525,12 +531,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
@@ -541,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="14">
-        <v>30545075.399999999</v>
+        <v>32801883.734994099</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -599,8 +605,8 @@
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14">
-        <v>3065244.36</v>
+      <c r="B5" s="7">
+        <v>3268487.8310066601</v>
       </c>
       <c r="E5" s="3">
         <v>2769333</v>
@@ -614,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="14">
-        <v>7401292</v>
+        <v>7301659.1604634598</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -647,7 +653,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="14">
-        <v>1626861.2661948199</v>
+        <v>1563426.905</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -657,12 +663,12 @@
       <c r="K11" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
@@ -690,22 +696,22 @@
         <v>0</v>
       </c>
       <c r="B15" s="14">
-        <v>30545075.399999999</v>
+        <v>31774489.069751099</v>
       </c>
       <c r="C15" s="14">
-        <v>30170030.661380101</v>
+        <v>31270061.068498202</v>
       </c>
       <c r="D15" s="14">
-        <v>29975328.866937201</v>
+        <v>32186826.551375002</v>
       </c>
       <c r="E15" s="14">
-        <v>29993363.038345698</v>
+        <v>31516253.983045101</v>
       </c>
       <c r="F15" s="14">
-        <v>30042764.404131401</v>
+        <v>31345975.0951389</v>
       </c>
       <c r="G15" s="14">
-        <v>30084216.821240999</v>
+        <v>31029385.726073898</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>22</v>
@@ -768,22 +774,22 @@
         <v>3</v>
       </c>
       <c r="B18" s="14">
-        <v>2673205.9300000002</v>
+        <v>2655895.5299999998</v>
       </c>
       <c r="C18" s="14">
-        <v>876913.8</v>
+        <v>984385.51599999995</v>
       </c>
       <c r="D18" s="14">
-        <v>362475.64</v>
+        <v>226051.66</v>
       </c>
       <c r="E18" s="14">
-        <v>223458.038</v>
+        <v>136779.97500000001</v>
       </c>
       <c r="F18" s="14">
-        <v>154271.15</v>
+        <v>55359.735999999997</v>
       </c>
       <c r="G18" s="14">
-        <v>129632.158</v>
+        <v>46494.372000000003</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -862,12 +868,12 @@
       <c r="G25" s="8"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
@@ -1044,13 +1050,24 @@
         <v>7</v>
       </c>
     </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G42" s="12"/>
+    </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
       <c r="E44" s="1"/>
       <c r="H44" s="3"/>
     </row>
@@ -1086,28 +1103,28 @@
         <v>0</v>
       </c>
       <c r="B46" s="14">
-        <v>30545075.399999999</v>
-      </c>
-      <c r="C46" s="13">
-        <v>60340061.32</v>
+        <v>32801883.734994099</v>
+      </c>
+      <c r="C46" s="14">
+        <v>62691950.200000003</v>
       </c>
       <c r="D46" s="14">
-        <v>89925986.609999999</v>
-      </c>
-      <c r="E46" s="13">
-        <v>119973452</v>
+        <v>94548761.939999998</v>
+      </c>
+      <c r="E46" s="14">
+        <v>128747306.2</v>
       </c>
       <c r="F46" s="14">
-        <v>150213822</v>
-      </c>
-      <c r="G46" s="13">
-        <v>180505301</v>
+        <v>156350305.34999999</v>
+      </c>
+      <c r="G46" s="14">
+        <v>186176314.38</v>
       </c>
       <c r="H46" s="14">
-        <v>209827302</v>
+        <v>222421423.49000001</v>
       </c>
       <c r="I46" s="13">
-        <v>240342115</v>
+        <v>240059496.08000001</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>5</v>
@@ -1150,28 +1167,28 @@
         <v>3</v>
       </c>
       <c r="B48" s="14">
-        <v>3065244.36</v>
+        <v>3268487.8310066601</v>
       </c>
       <c r="C48" s="14">
-        <v>3056406.42</v>
+        <v>3270697.1490000002</v>
       </c>
       <c r="D48" s="14">
-        <v>3071268.7</v>
+        <v>3291610.9</v>
       </c>
       <c r="E48" s="14">
-        <v>3057605.98</v>
+        <v>3295282.32</v>
       </c>
       <c r="F48" s="13">
-        <v>3049152.15</v>
+        <v>3308962.22</v>
       </c>
       <c r="G48" s="13">
-        <v>3062044.6</v>
+        <v>3311921.6189999999</v>
       </c>
       <c r="H48" s="13">
-        <v>3068963.78</v>
+        <v>3298082.798</v>
       </c>
       <c r="I48" s="13">
-        <v>3063581.93</v>
+        <v>3246734.8988999999</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>6</v>
@@ -1191,7 +1208,6 @@
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
       <c r="G50" s="12"/>
@@ -1204,16 +1220,16 @@
         <v>0</v>
       </c>
       <c r="B51" s="14">
-        <v>7401292</v>
+        <v>7301659.1604634598</v>
       </c>
       <c r="C51" s="14">
         <v>7439741</v>
       </c>
       <c r="D51" s="14">
+        <v>7531010</v>
+      </c>
+      <c r="E51" s="14">
         <v>7641958</v>
-      </c>
-      <c r="E51" s="14">
-        <v>7531010</v>
       </c>
       <c r="F51" s="14">
         <v>7664154</v>
@@ -1224,8 +1240,8 @@
       <c r="H51" s="14">
         <v>7689210</v>
       </c>
-      <c r="I51" s="14">
-        <v>7689210</v>
+      <c r="I51" s="17">
+        <v>7688381.2199999997</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>5</v>
@@ -1268,28 +1284,28 @@
         <v>3</v>
       </c>
       <c r="B53" s="14">
-        <v>1626861.2661948199</v>
+        <v>1563426.905</v>
       </c>
       <c r="C53" s="14">
-        <v>1621172.4051846999</v>
+        <v>1559000.38</v>
       </c>
       <c r="D53" s="14">
-        <v>1622474.0689999999</v>
+        <v>1565001.108</v>
       </c>
       <c r="E53" s="14">
-        <v>1626861.2661948199</v>
+        <v>1558914.97</v>
       </c>
       <c r="F53" s="14">
-        <v>1635437.8067000001</v>
+        <v>1558007.2</v>
       </c>
       <c r="G53" s="14">
-        <v>1627743.497</v>
+        <v>1555151.267</v>
       </c>
       <c r="H53" s="14">
-        <v>1624585.38</v>
+        <v>1543917.05</v>
       </c>
       <c r="I53" s="14">
-        <v>1621947.61</v>
+        <v>1566713.37</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>7</v>

--- a/results/section1.xlsx
+++ b/results/section1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="532"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020" tabRatio="532"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="36">
   <si>
     <t>Desis</t>
   </si>
@@ -100,6 +100,30 @@
   </si>
   <si>
     <t>byte</t>
+  </si>
+  <si>
+    <t>Throughput of root and intermedita nodes</t>
+  </si>
+  <si>
+    <t>root throughput</t>
+  </si>
+  <si>
+    <t>intermediate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tumling </t>
+  </si>
+  <si>
+    <t>root</t>
+  </si>
+  <si>
+    <t>Latency-single query</t>
+  </si>
+  <si>
+    <t>Total(NanoSec)</t>
+  </si>
+  <si>
+    <t>average</t>
   </si>
 </sst>
 </file>
@@ -129,7 +153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -152,11 +176,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -204,7 +241,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -511,38 +551,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P62"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P101"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.6328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.36328125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="14" width="8.88671875" style="2"/>
-    <col min="15" max="15" width="15.21875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="21.109375" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="2"/>
+    <col min="11" max="14" width="8.90625" style="2"/>
+    <col min="15" max="15" width="15.1796875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="21.08984375" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="1"/>
       <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -566,7 +606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -590,7 +630,7 @@
         <v>2991545</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
@@ -601,7 +641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
@@ -612,10 +652,10 @@
         <v>2769333</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
@@ -626,7 +666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
@@ -637,7 +677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>2</v>
       </c>
@@ -648,7 +688,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -656,21 +696,21 @@
         <v>1563426.905</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="F11" s="3">
         <v>2181646</v>
       </c>
       <c r="K11" s="5"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="7">
         <v>2</v>
@@ -691,7 +731,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>0</v>
       </c>
@@ -717,7 +757,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>1</v>
       </c>
@@ -743,7 +783,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>2</v>
       </c>
@@ -769,7 +809,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>3</v>
       </c>
@@ -792,7 +832,7 @@
         <v>46494.372000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
       <c r="B21" s="7">
         <v>1</v>
@@ -814,7 +854,7 @@
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>0</v>
       </c>
@@ -828,7 +868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>1</v>
       </c>
@@ -842,7 +882,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>2</v>
       </c>
@@ -856,7 +896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>3</v>
       </c>
@@ -867,15 +907,17 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="16" t="s">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A29" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="8"/>
       <c r="B30" s="8" t="s">
         <v>16</v>
@@ -889,7 +931,7 @@
       <c r="E30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="16" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="2" t="s">
@@ -897,160 +939,197 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="14">
         <v>11692164</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="14">
         <v>116</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="14">
         <v>116</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="14">
         <v>232</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="16" t="s">
         <v>5</v>
       </c>
       <c r="H31" s="9"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="14">
         <v>7480600</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="14">
         <v>3478</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="14">
         <v>3478</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="14">
         <v>6956</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="14">
+        <v>1681522</v>
+      </c>
+      <c r="C33" s="14">
+        <v>1601200000</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1601200000</v>
+      </c>
+      <c r="E33" s="14">
+        <v>3202400000</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B34" s="14">
         <v>1681522</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C34" s="14">
         <v>1601200000</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D34" s="14">
         <v>1601200000</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E34" s="14">
         <v>3202400000</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8" t="s">
+      <c r="F34" s="16"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D36" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E36" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F36" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H36" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" s="8">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="14">
         <v>11692164</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C37" s="14">
         <v>1600012168</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D37" s="14">
         <v>1601200000</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E37" s="14">
         <v>3201212168</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F37" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H37" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B38" s="14">
         <v>7480600</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C38" s="14">
         <v>1800039616</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D38" s="14">
         <v>1800039616</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E38" s="14">
         <v>3600079232</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F38" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="14">
+        <v>1681522</v>
+      </c>
+      <c r="C39" s="14">
+        <v>1601200000</v>
+      </c>
+      <c r="D39" s="14">
+        <v>1601200000</v>
+      </c>
+      <c r="E39" s="14">
+        <v>3202400000</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B40" s="14">
         <v>1681522</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C40" s="14">
         <v>1601200000</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D40" s="14">
         <v>1601200000</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E40" s="14">
         <v>3202400000</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F40" s="16"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
       <c r="E41" s="15"/>
@@ -1058,20 +1137,20 @@
       <c r="G41" s="15"/>
       <c r="H41" s="15"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="G42" s="12"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="16" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
       <c r="E44" s="1"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="11"/>
       <c r="B45" s="13">
         <v>1</v>
@@ -1098,7 +1177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
         <v>0</v>
       </c>
@@ -1130,7 +1209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
         <v>2</v>
       </c>
@@ -1162,194 +1241,222 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B48" s="14">
-        <v>3268487.8310066601</v>
-      </c>
-      <c r="C48" s="14">
-        <v>3270697.1490000002</v>
-      </c>
-      <c r="D48" s="14">
-        <v>3291610.9</v>
-      </c>
-      <c r="E48" s="14">
-        <v>3295282.32</v>
+        <v>9304926</v>
+      </c>
+      <c r="C48" s="13">
+        <v>9398916</v>
+      </c>
+      <c r="D48" s="13">
+        <v>9288468.0299999993</v>
+      </c>
+      <c r="E48" s="13">
+        <v>9394990</v>
       </c>
       <c r="F48" s="13">
-        <v>3308962.22</v>
+        <v>9246141.9600000009</v>
       </c>
       <c r="G48" s="13">
-        <v>3311921.6189999999</v>
+        <v>9281877.5715999994</v>
       </c>
       <c r="H48" s="13">
-        <v>3298082.798</v>
+        <v>9302153.9700000007</v>
       </c>
       <c r="I48" s="13">
-        <v>3246734.8988999999</v>
+        <v>9389027.4299999997</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="14">
+        <v>3268487.8310066601</v>
+      </c>
+      <c r="C49" s="14">
+        <v>3270697.1490000002</v>
+      </c>
+      <c r="D49" s="14">
+        <v>3291610.9</v>
+      </c>
+      <c r="E49" s="14">
+        <v>3295282.32</v>
+      </c>
+      <c r="F49" s="13">
+        <v>3308962.22</v>
+      </c>
+      <c r="G49" s="13">
+        <v>3311921.6189999999</v>
+      </c>
+      <c r="H49" s="13">
+        <v>3298082.798</v>
+      </c>
+      <c r="I49" s="13">
+        <v>3246734.8988999999</v>
+      </c>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12"/>
-      <c r="J50" s="6"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="14">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="6"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="14">
         <v>7301659.1604634598</v>
       </c>
-      <c r="C51" s="14">
-        <v>7439741</v>
-      </c>
-      <c r="D51" s="14">
-        <v>7531010</v>
-      </c>
-      <c r="E51" s="14">
-        <v>7641958</v>
-      </c>
-      <c r="F51" s="14">
-        <v>7664154</v>
-      </c>
-      <c r="G51" s="14">
-        <v>7681207</v>
-      </c>
-      <c r="H51" s="14">
-        <v>7689210</v>
-      </c>
-      <c r="I51" s="17">
-        <v>7688381.2199999997</v>
-      </c>
-      <c r="J51" s="6" t="s">
+      <c r="C53" s="14">
+        <v>7339741</v>
+      </c>
+      <c r="D53" s="14">
+        <v>7331010</v>
+      </c>
+      <c r="E53" s="14">
+        <v>7441958</v>
+      </c>
+      <c r="F53" s="14">
+        <v>7464154</v>
+      </c>
+      <c r="G53" s="14">
+        <v>7481207</v>
+      </c>
+      <c r="H53" s="14">
+        <v>7489210</v>
+      </c>
+      <c r="I53" s="14">
+        <v>7488381.2199999997</v>
+      </c>
+      <c r="J53" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B54" s="14">
         <v>40379</v>
       </c>
-      <c r="C52" s="14">
+      <c r="C54" s="14">
         <v>81010</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D54" s="14">
         <v>121524</v>
       </c>
-      <c r="E52" s="14">
+      <c r="E54" s="14">
         <v>162212</v>
       </c>
-      <c r="F52" s="14">
+      <c r="F54" s="14">
         <v>202755</v>
       </c>
-      <c r="G52" s="14">
+      <c r="G54" s="14">
         <v>243282</v>
       </c>
-      <c r="H52" s="14">
+      <c r="H54" s="14">
         <v>283521</v>
       </c>
-      <c r="I52" s="14">
+      <c r="I54" s="14">
         <v>324008</v>
       </c>
-      <c r="J52" s="6" t="s">
+      <c r="J54" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="14">
+        <v>7353263</v>
+      </c>
+      <c r="C55" s="13">
+        <v>7359730.3700000001</v>
+      </c>
+      <c r="D55" s="13">
+        <v>7352527</v>
+      </c>
+      <c r="E55" s="13">
+        <v>7356833</v>
+      </c>
+      <c r="F55" s="13">
+        <v>7369556</v>
+      </c>
+      <c r="G55" s="13">
+        <v>7342251</v>
+      </c>
+      <c r="H55" s="13">
+        <v>7352708</v>
+      </c>
+      <c r="I55" s="13">
+        <v>7367361</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B56" s="14">
         <v>1563426.905</v>
       </c>
-      <c r="C53" s="14">
+      <c r="C56" s="14">
         <v>1559000.38</v>
       </c>
-      <c r="D53" s="14">
+      <c r="D56" s="14">
         <v>1565001.108</v>
       </c>
-      <c r="E53" s="14">
+      <c r="E56" s="14">
         <v>1558914.97</v>
       </c>
-      <c r="F53" s="14">
+      <c r="F56" s="14">
         <v>1558007.2</v>
       </c>
-      <c r="G53" s="14">
+      <c r="G56" s="14">
         <v>1555151.267</v>
       </c>
-      <c r="H53" s="14">
+      <c r="H56" s="14">
         <v>1543917.05</v>
       </c>
-      <c r="I53" s="14">
+      <c r="I56" s="14">
         <v>1566713.37</v>
       </c>
-      <c r="J53" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D54" s="12"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="12"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B58" s="16"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
       <c r="I59" s="12"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
       <c r="E60" s="10"/>
@@ -1358,29 +1465,624 @@
       <c r="H60" s="10"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" s="16"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16"/>
       <c r="I61" s="12"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
+      <c r="J61" s="16"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="16"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="7"/>
+      <c r="B63" s="7">
+        <v>1</v>
+      </c>
+      <c r="C63" s="7">
+        <v>2</v>
+      </c>
+      <c r="D63" s="7">
+        <v>10</v>
+      </c>
+      <c r="E63" s="7">
+        <v>50</v>
+      </c>
+      <c r="F63" s="7">
+        <v>100</v>
+      </c>
+      <c r="G63" s="7">
+        <v>500</v>
+      </c>
+      <c r="H63" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I63" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J63" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" s="14">
+        <v>6213714.2300000004</v>
+      </c>
+      <c r="C64" s="14">
+        <v>6209130.7000000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>6232678.3300000001</v>
+      </c>
+      <c r="E64" s="14">
+        <v>6125299.9000000004</v>
+      </c>
+      <c r="F64" s="14">
+        <v>6133912.9500000002</v>
+      </c>
+      <c r="G64" s="18">
+        <v>6147710.9000000004</v>
+      </c>
+      <c r="H64" s="14">
+        <v>6083288.4699999997</v>
+      </c>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B65" s="14">
+        <v>6015109.3899999997</v>
+      </c>
+      <c r="C65" s="14">
+        <v>5976281.5999999996</v>
+      </c>
+      <c r="D65" s="14">
+        <v>5925974.71</v>
+      </c>
+      <c r="E65" s="14">
+        <v>5951692.9000000004</v>
+      </c>
+      <c r="F65" s="14">
+        <v>5919914.9100000001</v>
+      </c>
+      <c r="G65" s="18">
+        <v>5979043.8700000001</v>
+      </c>
+      <c r="H65" s="14">
+        <v>5898184.71</v>
+      </c>
+      <c r="I65" s="16"/>
+      <c r="J65" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="16"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="16"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="7"/>
+      <c r="B67" s="7">
+        <v>1</v>
+      </c>
+      <c r="C67" s="7">
+        <v>2</v>
+      </c>
+      <c r="D67" s="7">
+        <v>10</v>
+      </c>
+      <c r="E67" s="7">
+        <v>50</v>
+      </c>
+      <c r="F67" s="7">
+        <v>100</v>
+      </c>
+      <c r="G67" s="7">
+        <v>500</v>
+      </c>
+      <c r="H67" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I67" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="J67" s="16"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B68" s="14">
+        <v>16301088.8570717</v>
+      </c>
+      <c r="C68" s="14">
+        <v>16293672.2515093</v>
+      </c>
+      <c r="D68" s="14">
+        <v>16297227.102086</v>
+      </c>
+      <c r="E68" s="14">
+        <v>16299395.569248401</v>
+      </c>
+      <c r="F68" s="14">
+        <v>16300529.1725841</v>
+      </c>
+      <c r="G68" s="18">
+        <v>16297846.269078299</v>
+      </c>
+      <c r="H68" s="14">
+        <v>16294070.812556401</v>
+      </c>
+      <c r="I68" s="16"/>
+      <c r="J68" s="16"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B69" s="14">
+        <v>7441958</v>
+      </c>
+      <c r="C69" s="14">
+        <v>7464154</v>
+      </c>
+      <c r="D69" s="14">
+        <v>7481207</v>
+      </c>
+      <c r="E69" s="14">
+        <v>7489210</v>
+      </c>
+      <c r="F69" s="14">
+        <v>7488381.2199999997</v>
+      </c>
+      <c r="G69" s="14">
+        <v>7439741</v>
+      </c>
+      <c r="H69" s="14">
+        <v>7431010</v>
+      </c>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="16"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="14">
+        <v>108941</v>
+      </c>
+      <c r="C74" s="14">
+        <v>71705</v>
+      </c>
+      <c r="D74" s="14">
+        <v>137256</v>
+      </c>
+      <c r="E74" s="14">
+        <v>317902</v>
+      </c>
+      <c r="F74" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B75" s="14">
+        <v>227278</v>
+      </c>
+      <c r="C75" s="14">
+        <v>387587</v>
+      </c>
+      <c r="D75" s="14">
+        <v>341152</v>
+      </c>
+      <c r="E75" s="14">
+        <v>956017</v>
+      </c>
+      <c r="F75" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16">
+        <v>134282.33333333299</v>
+      </c>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B76" s="14">
+        <v>459361</v>
+      </c>
+      <c r="C76" s="14">
+        <v>0</v>
+      </c>
+      <c r="D76" s="14">
+        <v>0</v>
+      </c>
+      <c r="E76" s="14">
+        <v>459361</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="14">
+        <v>251758699</v>
+      </c>
+      <c r="C77" s="14">
+        <v>0</v>
+      </c>
+      <c r="D77" s="14">
+        <v>0</v>
+      </c>
+      <c r="E77" s="14">
+        <v>251758699</v>
+      </c>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" s="16"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
+      <c r="H78" s="16"/>
+      <c r="I78" s="16"/>
+      <c r="J78" s="16"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" s="14">
+        <v>5464357</v>
+      </c>
+      <c r="C80" s="14">
+        <v>6018705</v>
+      </c>
+      <c r="D80" s="14">
+        <v>116681</v>
+      </c>
+      <c r="E80" s="14">
+        <v>11599743</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G80" s="16"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="16"/>
+      <c r="J80" s="16"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" s="14">
+        <v>6195624</v>
+      </c>
+      <c r="C81" s="14">
+        <v>11012987</v>
+      </c>
+      <c r="D81" s="14">
+        <v>600179</v>
+      </c>
+      <c r="E81" s="14">
+        <v>17808790</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="16"/>
+      <c r="H81" s="16"/>
+      <c r="I81" s="16"/>
+      <c r="J81" s="16"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B82" s="14">
+        <v>5601264</v>
+      </c>
+      <c r="C82" s="14">
+        <v>0</v>
+      </c>
+      <c r="D82" s="14">
+        <v>0</v>
+      </c>
+      <c r="E82" s="14">
+        <v>5601264</v>
+      </c>
+      <c r="F82" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G82" s="16"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="16"/>
+      <c r="J82" s="16"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="14">
+        <v>420778408</v>
+      </c>
+      <c r="C83" s="14">
+        <v>0</v>
+      </c>
+      <c r="D83" s="14">
+        <v>0</v>
+      </c>
+      <c r="E83" s="14">
+        <v>420778408</v>
+      </c>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="16"/>
+      <c r="J83" s="16"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="16"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="16"/>
+      <c r="H84" s="16"/>
+      <c r="I84" s="16"/>
+      <c r="J84" s="16"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="16"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="16"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="16"/>
+      <c r="H85" s="16"/>
+      <c r="I85" s="16"/>
+      <c r="J85" s="16"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" s="16"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="16"/>
+      <c r="H86" s="16"/>
+      <c r="I86" s="16"/>
+      <c r="J86" s="16"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I87" s="16"/>
+      <c r="J87" s="16"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I88" s="16"/>
+      <c r="J88" s="16"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I89" s="16"/>
+      <c r="J89" s="16"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I90" s="16"/>
+      <c r="J90" s="16"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I92" s="16"/>
+      <c r="J92" s="16"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I93" s="16"/>
+      <c r="J93" s="16"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I94" s="16"/>
+      <c r="J94" s="16"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I95" s="16"/>
+      <c r="J95" s="16"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I96" s="16"/>
+      <c r="J96" s="16"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I97" s="16"/>
+      <c r="J97" s="16"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I98" s="16"/>
+      <c r="J98" s="16"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A99" s="16"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="16"/>
+      <c r="H99" s="16"/>
+      <c r="I99" s="16"/>
+      <c r="J99" s="16"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A100" s="16"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="16"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="16"/>
+      <c r="H100" s="16"/>
+      <c r="I100" s="16"/>
+      <c r="J100" s="16"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A101" s="16"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="16"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="16"/>
+      <c r="H101" s="16"/>
+      <c r="I101" s="16"/>
+      <c r="J101" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A62:D62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1389,9 +2091,202 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.08984375" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.90625" customWidth="1"/>
+    <col min="5" max="5" width="30.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="14">
+        <v>108941</v>
+      </c>
+      <c r="C3" s="14">
+        <v>71705</v>
+      </c>
+      <c r="D3" s="14">
+        <v>137256</v>
+      </c>
+      <c r="E3" s="14">
+        <v>317902</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14">
+        <v>227278</v>
+      </c>
+      <c r="C4" s="14">
+        <v>387587</v>
+      </c>
+      <c r="D4" s="14">
+        <v>41152</v>
+      </c>
+      <c r="E4" s="14">
+        <v>656017</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14">
+        <v>45936</v>
+      </c>
+      <c r="C5" s="14">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14">
+        <v>45936</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14">
+        <v>251758699</v>
+      </c>
+      <c r="C6" s="14">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14">
+        <v>251758699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="16"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="14">
+        <v>54643571</v>
+      </c>
+      <c r="C9" s="14">
+        <v>6018705</v>
+      </c>
+      <c r="D9" s="14">
+        <v>116681</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60778957</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="14">
+        <v>6195624</v>
+      </c>
+      <c r="C10" s="14">
+        <v>11012987</v>
+      </c>
+      <c r="D10" s="14">
+        <v>600179</v>
+      </c>
+      <c r="E10" s="14">
+        <v>17808790</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="14">
+        <v>60474</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60474</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420778408</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14">
+        <v>420778408</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1399,7 +2294,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
